--- a/docs/d/49/inyear.xlsx
+++ b/docs/d/49/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3810,8 +3810,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -7959,7 +7959,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>

--- a/docs/d/49/inyear.xlsx
+++ b/docs/d/49/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,11 @@
       <c r="AB27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -6297,7 +6301,11 @@
       <c r="AB54" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC54" s="4" t="inlineStr"/>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">

--- a/docs/d/49/inyear.xlsx
+++ b/docs/d/49/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2166,8 +2166,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -4329,8 +4329,8 @@
       <c r="W35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X35" s="9" t="n">
-        <v>0</v>
+      <c r="X35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y35" s="9" t="n">
         <v>0</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6173,8 +6173,8 @@
       <c r="S53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T53" s="9" t="n">
-        <v>0</v>
+      <c r="T53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U53" s="9" t="n">
         <v>0</v>
@@ -7835,7 +7835,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -8132,7 +8132,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>

--- a/docs/d/49/inyear.xlsx
+++ b/docs/d/49/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1233,8 +1233,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1750,8 +1750,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1855,8 +1855,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2271,8 +2271,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2574,8 +2574,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2889,8 +2889,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2994,8 +2994,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -3406,8 +3406,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="9" t="n">
         <v>0</v>
@@ -3606,8 +3606,8 @@
       <c r="W28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X28" s="9" t="n">
-        <v>2</v>
+      <c r="X28" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y28" s="9" t="n">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4125,8 +4125,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4535,8 +4535,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5152,13 +5152,13 @@
         <v>0</v>
       </c>
       <c r="X43" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5258,8 +5258,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>0</v>
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6603,8 +6603,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6708,8 +6708,8 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -7120,8 +7120,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="9" t="n">
         <v>0</v>
@@ -7736,7 +7736,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -7802,7 +7802,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -7835,7 +7835,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -7868,7 +7868,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -7901,7 +7901,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -8000,7 +8000,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -8066,7 +8066,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -8165,7 +8165,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>

--- a/docs/d/49/inyear.xlsx
+++ b/docs/d/49/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -967,17 +967,17 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M3" s="8" t="n">
@@ -1012,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="9" t="n">
         <v>0</v>
@@ -1278,17 +1278,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1383,17 +1383,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M7" s="8" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>1</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1900,13 +1900,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="9" t="n">
         <v>0</v>
@@ -1941,8 +1941,8 @@
       <c r="T12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U12" s="9" t="n">
-        <v>0</v>
+      <c r="U12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V12" s="9" t="n">
         <v>0</v>
@@ -2005,13 +2005,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2110,13 +2110,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2316,13 +2316,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2518,13 +2518,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2728,17 +2728,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2773,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2833,13 +2833,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2938,17 +2938,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3039,17 +3039,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3350,13 +3350,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>4</v>
       </c>
       <c r="W27" s="10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>5</v>
@@ -3556,13 +3556,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3657,13 +3657,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3859,13 +3859,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3964,13 +3964,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="P32" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q32" s="9" t="n">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4113,11 +4113,11 @@
       <c r="U33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="9" t="n">
-        <v>3</v>
+      <c r="V33" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" s="9" t="n">
         <v>3</v>
@@ -4174,13 +4174,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4378,13 +4378,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4479,13 +4479,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4580,13 +4580,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4685,13 +4685,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>0</v>
@@ -4786,17 +4786,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M40" s="8" t="n">
@@ -4891,17 +4891,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M41" s="8" t="n">
@@ -4996,13 +4996,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5101,13 +5101,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5202,13 +5202,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5246,11 +5246,11 @@
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="9" t="n">
-        <v>0</v>
+      <c r="V44" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" s="9" t="n">
         <v>2</v>
@@ -5412,13 +5412,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0</v>
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5618,13 +5618,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5723,13 +5723,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5828,13 +5828,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5929,13 +5929,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -6030,13 +6030,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6165,13 +6165,13 @@
         <v>1</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S53" s="9" t="n">
-        <v>0</v>
+      <c r="S53" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T53" s="10" t="n">
         <v>1</v>
@@ -6236,13 +6236,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6446,17 +6446,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6652,13 +6652,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6696,8 +6696,8 @@
       <c r="U58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="9" t="n">
-        <v>0</v>
+      <c r="V58" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6862,13 +6862,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6963,13 +6963,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7064,17 +7064,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -7165,13 +7165,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7266,13 +7266,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7371,13 +7371,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7476,13 +7476,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>7</v>
+        <v>-22</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7581,13 +7581,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -7802,7 +7802,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -7883,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7916,7 +7916,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -7967,7 +7967,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -8048,7 +8048,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -8066,7 +8066,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -8132,7 +8132,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -8165,7 +8165,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -8180,7 +8180,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -8213,7 +8213,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">

--- a/docs/d/49/inyear.xlsx
+++ b/docs/d/49/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/49/inyear.xlsx
+++ b/docs/d/49/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/49/inyear.xlsx
+++ b/docs/d/49/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/49/inyear.xlsx
+++ b/docs/d/49/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/49/inyear.xlsx
+++ b/docs/d/49/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -2833,13 +2833,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -6030,13 +6030,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="P54" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q54" s="10" t="n">
         <v>2</v>
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="9" t="n">
         <v>0</v>

--- a/docs/d/49/inyear.xlsx
+++ b/docs/d/49/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1723,8 +1723,8 @@
       <c r="P10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" s="9" t="n">
-        <v>1</v>
+      <c r="Q10" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R10" s="9" t="n">
         <v>0</v>
@@ -2316,13 +2316,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3489,8 +3489,8 @@
       <c r="S27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T27" s="9" t="n">
-        <v>0</v>
+      <c r="T27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U27" s="9" t="n">
         <v>0</v>
@@ -3657,13 +3657,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4891,13 +4891,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="S54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" s="10" t="n">
         <v>1</v>
@@ -7802,7 +7802,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -7934,7 +7934,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
